--- a/public/test-data/03_이전성과_5개년_테스트.xlsx
+++ b/public/test-data/03_이전성과_5개년_테스트.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R9d58c4cc81734763"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성과입력" sheetId="2" r:id="R818e387090274e01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R08ac8a8cbb46448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성과입력" sheetId="2" r:id="R0ffd2022613a446a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,7 +372,7 @@
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>5명 · 2021~2025년</x:v>
+        <x:v>5명 · 각 팀원의 승진심사 시기 직전 5개년</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
     </x:row>
@@ -442,7 +442,7 @@
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="21" t="str">
-        <x:v>팀원 5명 · 2021~2025년 업적(상/하)·역량 이력</x:v>
+        <x:v>팀원별 승진심사 시기 직전 5개년 업적(상/하)·역량 이력</x:v>
       </x:c>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -485,16 +485,16 @@
         <x:v>2029-09</x:v>
       </x:c>
       <x:c r="D5" s="28" t="n">
-        <x:v>2025</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="E5" s="27" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F5" s="27" t="str">
         <x:v>D</x:v>
       </x:c>
-      <x:c r="F5" s="27" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="G5" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
@@ -502,16 +502,16 @@
       <x:c r="B6" s="29" t="str"/>
       <x:c r="C6" s="29" t="str"/>
       <x:c r="D6" s="28" t="n">
-        <x:v>2024</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E6" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>S</x:v>
       </x:c>
       <x:c r="F6" s="27" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G6" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
@@ -519,7 +519,7 @@
       <x:c r="B7" s="29" t="str"/>
       <x:c r="C7" s="29" t="str"/>
       <x:c r="D7" s="28" t="n">
-        <x:v>2023</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E7" s="27" t="str">
         <x:v>B</x:v>
@@ -528,7 +528,7 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="G7" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
@@ -536,16 +536,16 @@
       <x:c r="B8" s="29" t="str"/>
       <x:c r="C8" s="29" t="str"/>
       <x:c r="D8" s="28" t="n">
-        <x:v>2022</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="E8" s="27" t="str">
+        <x:v>S</x:v>
+      </x:c>
+      <x:c r="F8" s="27" t="str">
         <x:v>D</x:v>
       </x:c>
-      <x:c r="F8" s="27" t="str">
-        <x:v>B</x:v>
-      </x:c>
       <x:c r="G8" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
@@ -553,16 +553,16 @@
       <x:c r="B9" s="29" t="str"/>
       <x:c r="C9" s="29" t="str"/>
       <x:c r="D9" s="28" t="n">
-        <x:v>2021</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="E9" s="27" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="F9" s="27" t="str">
         <x:v>S</x:v>
       </x:c>
-      <x:c r="F9" s="27" t="str">
-        <x:v>B</x:v>
-      </x:c>
       <x:c r="G9" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
@@ -576,16 +576,16 @@
         <x:v>2029-04</x:v>
       </x:c>
       <x:c r="D10" s="28" t="n">
-        <x:v>2025</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="E10" s="27" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="F10" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G10" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
@@ -593,16 +593,16 @@
       <x:c r="B11" s="29" t="str"/>
       <x:c r="C11" s="29" t="str"/>
       <x:c r="D11" s="28" t="n">
-        <x:v>2024</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E11" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>S</x:v>
       </x:c>
       <x:c r="F11" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="G11" s="27" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
@@ -610,16 +610,16 @@
       <x:c r="B12" s="29" t="str"/>
       <x:c r="C12" s="29" t="str"/>
       <x:c r="D12" s="28" t="n">
-        <x:v>2023</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E12" s="27" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="F12" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="G12" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
@@ -627,16 +627,16 @@
       <x:c r="B13" s="29" t="str"/>
       <x:c r="C13" s="29" t="str"/>
       <x:c r="D13" s="28" t="n">
-        <x:v>2022</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="E13" s="27" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="str">
         <x:v>S</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="G13" s="27" t="str">
-        <x:v>C</x:v>
+        <x:v>S</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
@@ -644,16 +644,16 @@
       <x:c r="B14" s="29" t="str"/>
       <x:c r="C14" s="29" t="str"/>
       <x:c r="D14" s="28" t="n">
-        <x:v>2021</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="E14" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F14" s="27" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="G14" s="27" t="str">
-        <x:v>C</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
@@ -667,13 +667,13 @@
         <x:v>2029-05</x:v>
       </x:c>
       <x:c r="D15" s="28" t="n">
-        <x:v>2025</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="E15" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F15" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="G15" s="27" t="str">
         <x:v>A</x:v>
@@ -684,16 +684,16 @@
       <x:c r="B16" s="29" t="str"/>
       <x:c r="C16" s="29" t="str"/>
       <x:c r="D16" s="28" t="n">
-        <x:v>2024</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E16" s="27" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F16" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="G16" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="21" customHeight="1">
@@ -701,16 +701,16 @@
       <x:c r="B17" s="29" t="str"/>
       <x:c r="C17" s="29" t="str"/>
       <x:c r="D17" s="28" t="n">
-        <x:v>2023</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E17" s="27" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F17" s="27" t="str">
-        <x:v>C</x:v>
+        <x:v>S</x:v>
       </x:c>
       <x:c r="G17" s="27" t="str">
-        <x:v>D</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21" customHeight="1">
@@ -718,16 +718,16 @@
       <x:c r="B18" s="29" t="str"/>
       <x:c r="C18" s="29" t="str"/>
       <x:c r="D18" s="28" t="n">
-        <x:v>2022</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="E18" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F18" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="G18" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
@@ -735,16 +735,16 @@
       <x:c r="B19" s="29" t="str"/>
       <x:c r="C19" s="29" t="str"/>
       <x:c r="D19" s="28" t="n">
-        <x:v>2021</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="E19" s="27" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F19" s="27" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G19" s="27" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21" customHeight="1">
@@ -758,16 +758,16 @@
         <x:v>2029-04</x:v>
       </x:c>
       <x:c r="D20" s="28" t="n">
-        <x:v>2025</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="E20" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F20" s="27" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G20" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
@@ -775,16 +775,16 @@
       <x:c r="B21" s="29" t="str"/>
       <x:c r="C21" s="29" t="str"/>
       <x:c r="D21" s="28" t="n">
-        <x:v>2024</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E21" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F21" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="G21" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
@@ -792,10 +792,10 @@
       <x:c r="B22" s="29" t="str"/>
       <x:c r="C22" s="29" t="str"/>
       <x:c r="D22" s="28" t="n">
-        <x:v>2023</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E22" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F22" s="27" t="str">
         <x:v>B</x:v>
@@ -809,16 +809,16 @@
       <x:c r="B23" s="29" t="str"/>
       <x:c r="C23" s="29" t="str"/>
       <x:c r="D23" s="28" t="n">
-        <x:v>2022</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="E23" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F23" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G23" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
@@ -826,16 +826,16 @@
       <x:c r="B24" s="29" t="str"/>
       <x:c r="C24" s="29" t="str"/>
       <x:c r="D24" s="28" t="n">
-        <x:v>2021</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="E24" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F24" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G24" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>S</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
@@ -849,7 +849,7 @@
         <x:v>2029-03</x:v>
       </x:c>
       <x:c r="D25" s="28" t="n">
-        <x:v>2025</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="E25" s="27" t="str">
         <x:v>A</x:v>
@@ -866,16 +866,16 @@
       <x:c r="B26" s="29" t="str"/>
       <x:c r="C26" s="29" t="str"/>
       <x:c r="D26" s="28" t="n">
-        <x:v>2024</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E26" s="27" t="str">
-        <x:v>D</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F26" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G26" s="27" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
@@ -883,16 +883,16 @@
       <x:c r="B27" s="29" t="str"/>
       <x:c r="C27" s="29" t="str"/>
       <x:c r="D27" s="28" t="n">
-        <x:v>2023</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E27" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F27" s="27" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="G27" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>D</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
@@ -900,16 +900,16 @@
       <x:c r="B28" s="29" t="str"/>
       <x:c r="C28" s="29" t="str"/>
       <x:c r="D28" s="28" t="n">
-        <x:v>2022</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="E28" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F28" s="27" t="str">
-        <x:v>S</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="G28" s="27" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
@@ -917,16 +917,16 @@
       <x:c r="B29" s="29" t="str"/>
       <x:c r="C29" s="29" t="str"/>
       <x:c r="D29" s="28" t="n">
-        <x:v>2021</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="E29" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F29" s="27" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="G29" s="27" t="str">
-        <x:v>B</x:v>
+        <x:v>S</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
